--- a/output/tables/eTable1_Human_AI_ADEs_Cohens_d.xlsx
+++ b/output/tables/eTable1_Human_AI_ADEs_Cohens_d.xlsx
@@ -13,9 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="60" uniqueCount="44">
-  <si>
-    <t>eTable 1. Effects of warning topics vs. control on perceived message effectiveness by sample, n=1,012 human participants and n=1,000 AI personas</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="62" uniqueCount="45">
+  <si>
+    <t>eTable 1. Effect of warning topic on perceived message effectiveness by sample, n=1,012 human participants and n=1,000 AI personas</t>
   </si>
   <si>
     <t>Human participants</t>
@@ -36,6 +36,12 @@
     <t>Cohen's d</t>
   </si>
   <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>[Referent]</t>
+  </si>
+  <si>
     <t>Addiction</t>
   </si>
   <si>
@@ -142,126 +148,114 @@
   </si>
   <si>
     <t>3.70</t>
-  </si>
-  <si>
-    <t>Note. ADE = average differential effect, estimated as the warning-topic coefficient from separate mixed-effects models with control as the reference category within each sample. Cohen's d was calculated using the Campbell HLM/mixed-effects formula.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="25">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <i/>
+  <fonts count="23">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <b/>
     </font>
   </fonts>
   <fills count="2">
@@ -272,7 +266,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -364,18 +358,11 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
@@ -422,10 +409,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -484,163 +467,169 @@
       <c r="B4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
-        <v>10</v>
-      </c>
       <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="s">
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
         <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" t="s">
+      <c r="F6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
         <v>19</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" t="s">
         <v>23</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
         <v>24</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" t="s">
         <v>28</v>
       </c>
-      <c r="B8" t="s">
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
         <v>29</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
         <v>33</v>
       </c>
-      <c r="B9" t="s">
+      <c r="F9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
         <v>38</v>
       </c>
-      <c r="B10" t="s">
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
-        <v>9</v>
-      </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>40</v>
       </c>
-      <c r="E10" t="s">
+      <c r="B11" t="s">
         <v>41</v>
       </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="s">
+      <c r="E11" t="s">
         <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
